--- a/static/openproject_timesheet_sample.xlsx
+++ b/static/openproject_timesheet_sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lokesh V\Automation\openproject\openproject\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lokesh V\Automation\openproject\openproject_automation-main\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2244B8B7-56C9-4336-A395-FCDE7E4EC1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2D434C-6F67-44DF-93B8-4332A0844E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="Login Details" sheetId="1" r:id="rId1"/>
     <sheet name="Time Sheet" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -116,11 +129,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -479,10 +491,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -534,7 +546,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -547,7 +559,8 @@
         <v>5</v>
       </c>
       <c r="E2" s="2">
-        <v>46023</v>
+        <f ca="1">WORKDAY(EOMONTH(TODAY(),-1),ROW(A2))</f>
+        <v>46297</v>
       </c>
       <c r="F2" s="1">
         <v>8</v>
@@ -558,7 +571,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -571,7 +584,8 @@
         <v>5</v>
       </c>
       <c r="E3" s="2">
-        <v>46024</v>
+        <f ca="1">WORKDAY(EOMONTH(TODAY(),-1),ROW(A3))</f>
+        <v>46300</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
